--- a/data/trans_dic/P2A_senso_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,5</t>
+          <t>2,34; 4,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,43</t>
+          <t>1,31; 3,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,91</t>
+          <t>0,79; 2,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,02</t>
+          <t>2,02; 5,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,51</t>
+          <t>1,86; 3,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,34</t>
+          <t>1,62; 3,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,62</t>
+          <t>0,9; 2,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,28</t>
+          <t>4,64; 7,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,8</t>
+          <t>2,37; 3,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,97</t>
+          <t>1,69; 2,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,39</t>
+          <t>1,06; 2,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,94</t>
+          <t>3,99; 5,94</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,26</t>
+          <t>0,38; 1,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,15</t>
+          <t>1,02; 2,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,42</t>
+          <t>0,5; 1,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,86</t>
+          <t>1,39; 2,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,75</t>
+          <t>0,63; 1,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,55</t>
+          <t>1,08; 2,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,5</t>
+          <t>0,63; 1,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 35,95</t>
+          <t>2,11; 33,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,28</t>
+          <t>0,59; 1,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,05</t>
+          <t>1,2; 2,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,34</t>
+          <t>0,67; 1,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 22,56</t>
+          <t>2,01; 21,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,03</t>
+          <t>0,19; 1,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,34</t>
+          <t>0,59; 3,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,65</t>
+          <t>0,17; 1,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,04</t>
+          <t>1,01; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,2</t>
+          <t>0,41; 2,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,05</t>
+          <t>1,86; 6,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,43</t>
+          <t>0,98; 2,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,76</t>
+          <t>0,39; 1,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,77</t>
+          <t>1,49; 3,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,07</t>
+          <t>0,18; 1,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,41</t>
+          <t>1,2; 2,49</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,02</t>
+          <t>1,15; 2,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,24</t>
+          <t>1,31; 2,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,45</t>
+          <t>0,7; 1,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,8</t>
+          <t>1,65; 2,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,17</t>
+          <t>1,28; 2,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,78</t>
+          <t>1,7; 2,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,49</t>
+          <t>0,75; 1,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 25,65</t>
+          <t>2,8; 25,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,92</t>
+          <t>1,32; 1,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,29</t>
+          <t>1,6; 2,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,34</t>
+          <t>0,82; 1,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 15,46</t>
+          <t>2,45; 16,56</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23678; 46399</t>
+          <t>24093; 46436</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13049; 33439</t>
+          <t>12806; 32768</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6257; 21983</t>
+          <t>5935; 21025</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10642; 25826</t>
+          <t>10388; 25790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23746; 46193</t>
+          <t>24427; 48269</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22156; 44722</t>
+          <t>21688; 43809</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8568; 26090</t>
+          <t>8991; 26675</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36483; 54965</t>
+          <t>35080; 54600</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54700; 89079</t>
+          <t>55604; 87953</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39764; 68752</t>
+          <t>39126; 68918</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17480; 41791</t>
+          <t>18626; 41829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50970; 75506</t>
+          <t>50640; 75476</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6504; 21264</t>
+          <t>6401; 20405</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19741; 42320</t>
+          <t>20081; 43110</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10638; 29574</t>
+          <t>10413; 30955</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31837; 65505</t>
+          <t>31829; 66594</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9765; 27713</t>
+          <t>10020; 26754</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20131; 44907</t>
+          <t>18954; 42570</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12197; 29781</t>
+          <t>12568; 30239</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46251; 804430</t>
+          <t>47114; 740535</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20041; 41952</t>
+          <t>19235; 41267</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44452; 76322</t>
+          <t>44517; 76500</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26680; 54345</t>
+          <t>27118; 52969</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91723; 1021676</t>
+          <t>90801; 982589</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1066; 11167</t>
+          <t>1055; 10947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1958; 16080</t>
+          <t>2853; 18701</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>949; 9012</t>
+          <t>951; 9210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6423; 19637</t>
+          <t>6532; 20037</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1932; 10486</t>
+          <t>1947; 11109</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9035; 27760</t>
+          <t>8543; 27735</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6846</t>
+          <t>0; 5805</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6123; 16045</t>
+          <t>6492; 16496</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4877; 18068</t>
+          <t>4049; 17306</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13500; 35395</t>
+          <t>13969; 35207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1982; 11704</t>
+          <t>1999; 12270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15086; 31509</t>
+          <t>15631; 32498</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38003; 66259</t>
+          <t>37661; 66661</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44892; 76601</t>
+          <t>44740; 77732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23595; 48898</t>
+          <t>23609; 49377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54201; 96586</t>
+          <t>56818; 96302</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42733; 73473</t>
+          <t>43136; 72447</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60302; 98723</t>
+          <t>60347; 95422</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26718; 52548</t>
+          <t>26449; 51435</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101559; 937156</t>
+          <t>102313; 917779</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86200; 127504</t>
+          <t>87814; 127417</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113309; 160037</t>
+          <t>111499; 160559</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55658; 92274</t>
+          <t>56346; 90847</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>174249; 1098750</t>
+          <t>173739; 1177030</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,5</t>
+          <t>2,33; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,36</t>
+          <t>1,46; 3,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,79</t>
+          <t>0,85; 2,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,01</t>
+          <t>1,95; 4,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,67</t>
+          <t>1,81; 3,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,27</t>
+          <t>1,64; 3,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,68</t>
+          <t>0,91; 2,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,23</t>
+          <t>4,99; 7,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,75</t>
+          <t>2,28; 3,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,98</t>
+          <t>1,69; 3,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,39</t>
+          <t>1,04; 2,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 5,94</t>
+          <t>4,07; 5,91</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,2</t>
+          <t>0,39; 1,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,2</t>
+          <t>0,98; 2,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,49</t>
+          <t>0,47; 1,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,91</t>
+          <t>1,91; 3,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,69</t>
+          <t>0,63; 1,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,42</t>
+          <t>1,13; 2,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,52</t>
+          <t>0,63; 1,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 33,09</t>
+          <t>2,08; 3,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,26</t>
+          <t>0,6; 1,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,06</t>
+          <t>1,23; 2,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,3</t>
+          <t>0,64; 1,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 21,7</t>
+          <t>2,13; 3,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,99</t>
+          <t>0,19; 2,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,89</t>
+          <t>0,45; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,68</t>
+          <t>0,18; 1,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,1</t>
+          <t>1,04; 3,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,33</t>
+          <t>0,41; 2,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,05</t>
+          <t>1,87; 5,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,5</t>
+          <t>1,12; 2,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,68</t>
+          <t>0,39; 1,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,75</t>
+          <t>1,39; 3,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,12</t>
+          <t>0,18; 1,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,49</t>
+          <t>1,2; 2,44</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,03</t>
+          <t>1,15; 2,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,27</t>
+          <t>1,31; 2,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,46</t>
+          <t>0,7; 1,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,79</t>
+          <t>1,95; 3,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,14</t>
+          <t>1,27; 2,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,68</t>
+          <t>1,66; 2,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,46</t>
+          <t>0,74; 1,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 25,12</t>
+          <t>2,72; 3,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,91</t>
+          <t>1,32; 1,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,3</t>
+          <t>1,6; 2,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,31</t>
+          <t>0,81; 1,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 16,56</t>
+          <t>2,53; 3,25</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16786</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45053</t>
+          <t>50561</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61838</t>
+          <t>68680</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24093; 46436</t>
+          <t>24032; 48026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12806; 32768</t>
+          <t>14256; 35071</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5935; 21025</t>
+          <t>6418; 22088</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10388; 25790</t>
+          <t>11310; 27846</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24427; 48269</t>
+          <t>23759; 47225</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21688; 43809</t>
+          <t>22000; 43568</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8991; 26675</t>
+          <t>9037; 26433</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35080; 54600</t>
+          <t>41030; 63464</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55604; 87953</t>
+          <t>53428; 84904</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39126; 68918</t>
+          <t>39066; 69968</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18626; 41829</t>
+          <t>18204; 42308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50640; 75476</t>
+          <t>56995; 82782</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>56416</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>251331</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>298756</t>
+          <t>113095</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6401; 20405</t>
+          <t>6627; 21440</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20081; 43110</t>
+          <t>19305; 41386</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10413; 30955</t>
+          <t>9847; 28772</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31829; 66594</t>
+          <t>42530; 75432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10020; 26754</t>
+          <t>9981; 27053</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18954; 42570</t>
+          <t>19819; 42964</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12568; 30239</t>
+          <t>12438; 31419</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47114; 740535</t>
+          <t>45069; 72544</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19235; 41267</t>
+          <t>19752; 41887</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44517; 76500</t>
+          <t>45636; 79786</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27118; 52969</t>
+          <t>25874; 51541</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90801; 982589</t>
+          <t>93774; 136276</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>25579</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1055; 10947</t>
+          <t>1060; 11001</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2853; 18701</t>
+          <t>2147; 16057</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>951; 9210</t>
+          <t>960; 8840</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6532; 20037</t>
+          <t>7428; 22548</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1947; 11109</t>
+          <t>1951; 10994</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8543; 27735</t>
+          <t>8565; 26277</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5805</t>
+          <t>0; 6288</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6492; 16496</t>
+          <t>8231; 19262</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4049; 17306</t>
+          <t>4024; 17436</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13969; 35207</t>
+          <t>13068; 35374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1999; 12270</t>
+          <t>1931; 11633</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15631; 32498</t>
+          <t>17362; 35242</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76052</t>
+          <t>87137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>307037</t>
+          <t>120218</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>383089</t>
+          <t>207354</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37661; 66661</t>
+          <t>37702; 65606</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44740; 77732</t>
+          <t>44885; 75358</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23609; 49377</t>
+          <t>23651; 49784</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56818; 96302</t>
+          <t>68822; 109171</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43136; 72447</t>
+          <t>43055; 73542</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60347; 95422</t>
+          <t>59141; 97084</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26449; 51435</t>
+          <t>26176; 51679</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>102313; 917779</t>
+          <t>101278; 140115</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87814; 127417</t>
+          <t>87785; 127834</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111499; 160559</t>
+          <t>111870; 160873</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56346; 90847</t>
+          <t>55813; 91716</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>173739; 1177030</t>
+          <t>183507; 235458</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
